--- a/data/trans_dic/P2A_fisi_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación, discapacidad física</t>
+          <t>Hogares con personas con limitación, discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,11</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>0,0; 9,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,23</t>
+          <t>1,35; 10,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,73</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,26</t>
+          <t>0,0; 11,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 18,8</t>
+          <t>2,33; 18,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 13,53</t>
+          <t>2,32; 14,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,99</t>
+          <t>1,79; 11,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,92</t>
+          <t>0,59; 5,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 12,47</t>
+          <t>1,92; 11,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,98</t>
+          <t>2,58; 10,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,09</t>
+          <t>1,24; 6,63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,04</t>
+          <t>0,86; 7,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,11</t>
+          <t>0,0; 12,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,74</t>
+          <t>2,0; 11,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,48</t>
+          <t>0,97; 9,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 11,78</t>
+          <t>2,07; 10,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,14</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 11,39</t>
+          <t>2,51; 10,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,53</t>
+          <t>1,36; 6,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,06</t>
+          <t>1,13; 7,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,41</t>
+          <t>0,48; 5,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,31</t>
+          <t>2,89; 9,02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,24</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 9,28</t>
+          <t>0,88; 9,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,36</t>
+          <t>0,0; 6,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,7</t>
+          <t>0,0; 8,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 15,86</t>
+          <t>4,82; 16,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,38</t>
+          <t>0,65; 5,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,74</t>
+          <t>4,09; 11,26</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 7,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 7,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 12,48</t>
+          <t>1,36; 13,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,22</t>
+          <t>1,21; 10,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,99</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 13,53</t>
+          <t>1,42; 13,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,58</t>
+          <t>0,42; 3,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,41</t>
+          <t>0,68; 6,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,98</t>
+          <t>0,82; 7,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,55</t>
+          <t>0,96; 8,0</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,39</t>
+          <t>0,0; 28,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,03</t>
+          <t>0,0; 23,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 12,54</t>
+          <t>1,02; 11,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,08</t>
+          <t>0,0; 13,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,09</t>
+          <t>0,0; 12,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,9</t>
+          <t>0,0; 8,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,53</t>
+          <t>0,0; 16,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 12,56</t>
+          <t>1,48; 12,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,86</t>
+          <t>0,0; 7,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,15</t>
+          <t>1,08; 8,07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 15,02</t>
+          <t>1,69; 13,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,92</t>
+          <t>0,0; 15,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 17,3</t>
+          <t>4,26; 17,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,64</t>
+          <t>0,0; 9,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,54</t>
+          <t>0,0; 9,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,49</t>
+          <t>0,0; 11,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,23; 22,08</t>
+          <t>7,58; 21,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 9,16</t>
+          <t>1,97; 8,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,33</t>
+          <t>1,1; 9,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 17,38</t>
+          <t>7,63; 17,42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,96</t>
+          <t>0,62; 6,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,24</t>
+          <t>1,62; 8,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,44</t>
+          <t>0,66; 6,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 14,94</t>
+          <t>5,55; 14,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,64</t>
+          <t>1,48; 7,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,14</t>
+          <t>0,51; 4,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 8,34</t>
+          <t>1,16; 8,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 17,61</t>
+          <t>2,94; 16,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,66</t>
+          <t>1,57; 5,43</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,52</t>
+          <t>1,53; 5,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,68</t>
+          <t>1,52; 5,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 12,85</t>
+          <t>5,15; 13,6</t>
         </is>
       </c>
     </row>
@@ -1696,27 +1697,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,71</t>
+          <t>0,7; 6,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,93</t>
+          <t>0,51; 4,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,59</t>
+          <t>0,95; 6,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,63</t>
+          <t>1,9; 7,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,27; 11,55</t>
+          <t>2,88; 11,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1726,32 +1727,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 7,42</t>
+          <t>1,35; 7,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,66</t>
+          <t>2,63; 7,95</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,93</t>
+          <t>1,36; 4,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,62</t>
+          <t>0,7; 3,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,33</t>
+          <t>2,15; 5,99</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,97</t>
+          <t>0,96; 2,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,25</t>
+          <t>1,76; 4,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,16</t>
+          <t>1,55; 4,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,84</t>
+          <t>3,72; 6,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,87</t>
+          <t>2,24; 4,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,99</t>
+          <t>2,48; 5,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,41</t>
+          <t>1,32; 3,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,44</t>
+          <t>4,59; 8,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,55</t>
+          <t>1,95; 3,62</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,11</t>
+          <t>2,33; 4,1</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,3</t>
+          <t>1,72; 3,37</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,95</t>
+          <t>4,59; 7,0</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con limitación, discapacidad física (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1913</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2962</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3936</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3464</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5181</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4655</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3339</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2323</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>615; 4619</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3869</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5863</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>886; 6990</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1208; 7385</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1421; 9096</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>580; 5604</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1220; 7228</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2510; 9744</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1893; 10126</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7574</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2504</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3153</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7184</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4336</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3781</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3348</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>14758</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>581; 4920</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 8631</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2556; 14175</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>632; 6217</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1217; 6388</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5032</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3204; 13918</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1802; 8437</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1284; 8180</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>723; 8774</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7378; 23019</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2255</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1489</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6360</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2276</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8615</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4889</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>514; 5320</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4388</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5301</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3235; 11285</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4418</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>738; 6118</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5136; 14119</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3847</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2064</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2963</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4453</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4673</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3530</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>611; 5946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2901</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4211</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>674; 5826</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3749</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1112; 10428</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>591; 5375</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>720; 6370</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>760; 6762</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1426; 11867</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1481</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2758</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4185</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>351; 3917</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3271</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4591</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3621</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3448</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>631; 5443</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4829</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>814; 6074</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2651</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4413</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>7630</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>12043</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>751; 6201</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4133</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1967; 8121</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4969</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4929</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3630</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>4260; 12271</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4851</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1853; 8431</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>644; 5829</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>7811; 17833</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2770</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4661</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3018</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>11853</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>4225</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2520</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4215</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>10498</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>6995</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>7181</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>7232</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>22352</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>690; 6934</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1891; 9976</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>768; 7213</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6908; 18161</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1639; 8426</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>627; 6077</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1377; 9953</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>4591; 25237</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>3475; 12015</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3650; 13134</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3593; 13458</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>14455; 38138</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3314</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5223</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6249</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>4868</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>5839</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>8453</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>6827</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4704</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>11061</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>631; 5789</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>585; 5218</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1234; 7855</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2506; 9882</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2778; 11177</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1980; 9489</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4922</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2120; 11263</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>4914; 14852</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>3353; 11944</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>1884; 9259</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>6205; 17272</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>8948</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>13156</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>13758</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>34124</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>18269</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>19165</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>12645</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>46113</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>27217</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>32322</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>26402</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>80237</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>4835; 14749</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>8417; 21328</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>8157; 21193</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>24780; 44047</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>11828; 25565</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>13359; 27717</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>7533; 18987</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>34970; 62420</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>20139; 37367</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>23632; 41632</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>18841; 36896</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>65572; 100011</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_fisi_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,0; 6,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,16</t>
+          <t>0,0; 9,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 10,18</t>
+          <t>1,37; 11,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,28</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,46</t>
+          <t>0,0; 10,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 18,36</t>
+          <t>1,69; 17,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 14,2</t>
+          <t>2,3; 13,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 11,46</t>
+          <t>1,64; 11,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,67</t>
+          <t>0,58; 5,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,39</t>
+          <t>1,7; 12,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,01</t>
+          <t>2,33; 10,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,63</t>
+          <t>1,32; 6,46</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,21</t>
+          <t>0,0; 10,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,1</t>
+          <t>2,32; 11,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,57</t>
+          <t>0,99; 9,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 10,85</t>
+          <t>2,08; 11,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 10,91</t>
+          <t>2,39; 11,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,35</t>
+          <t>1,4; 6,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,22</t>
+          <t>1,14; 7,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,82</t>
+          <t>0,48; 6,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,02</t>
+          <t>3,1; 9,41</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 10,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,13</t>
+          <t>1,07; 9,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,46</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,84</t>
+          <t>0,0; 7,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 16,8</t>
+          <t>4,82; 16,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,43</t>
+          <t>0,66; 5,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,26</t>
+          <t>4,0; 11,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,07</t>
+          <t>0,0; 6,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 13,18</t>
+          <t>1,34; 12,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 5,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,5</t>
+          <t>1,19; 10,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 6,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,35</t>
+          <t>1,32; 13,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,85</t>
+          <t>0,42; 4,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,06</t>
+          <t>0,67; 6,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,29</t>
+          <t>0,82; 7,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,0</t>
+          <t>0,91; 6,91</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,91</t>
+          <t>0,0; 31,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,19</t>
+          <t>0,0; 23,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 11,35</t>
+          <t>1,05; 12,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,28</t>
+          <t>0,0; 10,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,93</t>
+          <t>0,0; 10,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,89</t>
+          <t>0,0; 9,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,46</t>
+          <t>0,0; 16,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 12,76</t>
+          <t>1,47; 11,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,11</t>
+          <t>0,0; 7,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 8,07</t>
+          <t>0,94; 7,18</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 13,92</t>
+          <t>1,64; 14,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,15</t>
+          <t>0,0; 15,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,26; 17,59</t>
+          <t>4,51; 17,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,51</t>
+          <t>0,0; 8,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,95</t>
+          <t>0,0; 10,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,58</t>
+          <t>0,0; 11,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,58; 21,84</t>
+          <t>8,11; 23,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,96</t>
+          <t>1,96; 8,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,94</t>
+          <t>1,08; 10,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,63; 17,42</t>
+          <t>7,09; 17,32</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,27</t>
+          <t>0,62; 5,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,55</t>
+          <t>1,67; 8,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,18</t>
+          <t>0,66; 6,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,55; 14,59</t>
+          <t>5,57; 15,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,61</t>
+          <t>1,32; 8,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,99</t>
+          <t>0,51; 5,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 8,36</t>
+          <t>1,14; 7,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,18</t>
+          <t>3,03; 17,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,43</t>
+          <t>1,59; 5,62</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,51</t>
+          <t>1,51; 5,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,71</t>
+          <t>1,49; 5,65</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 13,6</t>
+          <t>5,1; 13,1</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,42</t>
+          <t>0,7; 6,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,52</t>
+          <t>0,5; 4,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,06</t>
+          <t>0,94; 5,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,51</t>
+          <t>1,96; 7,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,88; 11,57</t>
+          <t>3,59; 12,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,27</t>
+          <t>1,61; 7,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,54</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,18</t>
+          <t>1,82; 7,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,95</t>
+          <t>2,61; 7,74</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,86</t>
+          <t>1,37; 4,92</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,44</t>
+          <t>0,76; 3,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,99</t>
+          <t>2,14; 6,12</t>
         </is>
       </c>
     </row>
@@ -1837,52 +1837,52 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,93</t>
+          <t>1,0; 2,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,47</t>
+          <t>1,8; 4,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,03</t>
+          <t>1,57; 4,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,61</t>
+          <t>3,96; 6,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,84</t>
+          <t>2,3; 5,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,14</t>
+          <t>2,37; 5,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,33</t>
+          <t>1,28; 3,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,19</t>
+          <t>4,5; 8,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,62</t>
+          <t>1,89; 3,56</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,1</t>
+          <t>2,39; 4,15</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,0</t>
+          <t>4,47; 6,93</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3339</t>
+          <t>0; 2952</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2323</t>
+          <t>0; 2331</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>615; 4619</t>
+          <t>623; 5415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3869</t>
+          <t>0; 3306</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5863</t>
+          <t>0; 5121</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>886; 6990</t>
+          <t>643; 6504</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1208; 7385</t>
+          <t>1198; 7164</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1421; 9096</t>
+          <t>1302; 8737</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>580; 5604</t>
+          <t>578; 5637</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1220; 7228</t>
+          <t>1081; 7894</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2510; 9744</t>
+          <t>2268; 9965</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1893; 10126</t>
+          <t>2009; 9854</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>581; 4920</t>
+          <t>587; 4923</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3458</t>
+          <t>0; 3153</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8631</t>
+          <t>0; 7192</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2556; 14175</t>
+          <t>2967; 14052</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>632; 6217</t>
+          <t>645; 5926</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1217; 6388</t>
+          <t>1222; 6897</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5032</t>
+          <t>0; 4231</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3204; 13918</t>
+          <t>3050; 14091</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1802; 8437</t>
+          <t>1859; 8709</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1284; 8180</t>
+          <t>1292; 8045</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>723; 8774</t>
+          <t>729; 9212</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7378; 23019</t>
+          <t>7916; 24010</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4889</t>
+          <t>0; 5425</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>514; 5320</t>
+          <t>622; 5512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4388</t>
+          <t>0; 4352</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5301</t>
+          <t>0; 4499</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3235; 11285</t>
+          <t>3235; 11131</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4418</t>
+          <t>0; 3957</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>738; 6118</t>
+          <t>740; 6160</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5136; 14119</t>
+          <t>5014; 14551</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4673</t>
+          <t>0; 3982</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3530</t>
+          <t>0; 3072</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>611; 5946</t>
+          <t>603; 5683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2901</t>
+          <t>0; 2500</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4211</t>
+          <t>0; 4176</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>674; 5826</t>
+          <t>662; 5831</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3749</t>
+          <t>0; 3115</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1112; 10428</t>
+          <t>1032; 10828</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>591; 5375</t>
+          <t>582; 6119</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>720; 6370</t>
+          <t>701; 6924</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>760; 6762</t>
+          <t>761; 7358</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1426; 11867</t>
+          <t>1351; 10248</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2758</t>
+          <t>0; 3000</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>0; 4284</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>351; 3917</t>
+          <t>362; 4201</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,37 +3066,37 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3271</t>
+          <t>0; 2691</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4591</t>
+          <t>0; 3787</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3621</t>
+          <t>0; 3941</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3448</t>
+          <t>0; 3486</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>631; 5443</t>
+          <t>629; 5073</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4829</t>
+          <t>0; 5106</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>814; 6074</t>
+          <t>709; 5403</t>
         </is>
       </c>
     </row>
@@ -3254,57 +3254,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>751; 6201</t>
+          <t>729; 6295</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4133</t>
+          <t>0; 4215</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1967; 8121</t>
+          <t>2082; 8220</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4969</t>
+          <t>0; 4467</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4929</t>
+          <t>0; 4989</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3630</t>
+          <t>0; 3754</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4260; 12271</t>
+          <t>4556; 13032</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4851</t>
+          <t>0; 5331</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1853; 8431</t>
+          <t>1846; 8008</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>644; 5829</t>
+          <t>631; 6156</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7811; 17833</t>
+          <t>7254; 17726</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>690; 6934</t>
+          <t>687; 6252</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1891; 9976</t>
+          <t>1947; 9513</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>768; 7213</t>
+          <t>775; 7460</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6908; 18161</t>
+          <t>6930; 18822</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1639; 8426</t>
+          <t>1461; 8957</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>627; 6077</t>
+          <t>627; 6325</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1377; 9953</t>
+          <t>1360; 9515</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4591; 25237</t>
+          <t>4732; 27236</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3475; 12015</t>
+          <t>3520; 12452</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3650; 13134</t>
+          <t>3591; 12975</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3593; 13458</t>
+          <t>3517; 13339</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14455; 38138</t>
+          <t>14304; 36735</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>631; 5789</t>
+          <t>632; 5921</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>585; 5218</t>
+          <t>581; 5266</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1234; 7855</t>
+          <t>1222; 7620</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2506; 9882</t>
+          <t>2582; 10234</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2778; 11177</t>
+          <t>3468; 11721</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1980; 9489</t>
+          <t>2095; 9782</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 4922</t>
+          <t>0; 4801</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2120; 11263</t>
+          <t>2850; 12306</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4914; 14852</t>
+          <t>4865; 14462</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3353; 11944</t>
+          <t>3363; 12101</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1884; 9259</t>
+          <t>2045; 9974</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6205; 17272</t>
+          <t>6175; 17661</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4835; 14749</t>
+          <t>5012; 15030</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8417; 21328</t>
+          <t>8595; 20541</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8157; 21193</t>
+          <t>8253; 21186</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24780; 44047</t>
+          <t>26360; 45360</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11828; 25565</t>
+          <t>12140; 26620</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13359; 27717</t>
+          <t>12767; 27542</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7533; 18987</t>
+          <t>7317; 19810</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>34970; 62420</t>
+          <t>34286; 61958</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>20139; 37367</t>
+          <t>19548; 36688</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>23632; 41632</t>
+          <t>24241; 42138</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18841; 36896</t>
+          <t>18841; 36956</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>65572; 100011</t>
+          <t>63892; 99037</t>
         </is>
       </c>
     </row>
